--- a/oferte_butoaie.xlsx
+++ b/oferte_butoaie.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="94">
   <si>
     <t>BUC</t>
   </si>
@@ -174,9 +174,6 @@
     <t xml:space="preserve">RAV SMP 5W30 60L </t>
   </si>
   <si>
-    <t>RAV VMO 5W40 60L CUSTODIE</t>
-  </si>
-  <si>
     <t>RAV ATF DEXRON III H 20L</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
   </si>
   <si>
     <t>ADAOS 30%</t>
-  </si>
-  <si>
-    <t>RAV SMP 5W30 60L CUSTODIE</t>
   </si>
   <si>
     <t>VAL HLP 46 20L</t>
@@ -1648,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.5703125" customWidth="1"/>
@@ -1666,13 +1660,13 @@
         <v>27</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E1" s="38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1695,7 +1689,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="26">
         <v>2</v>
@@ -1704,7 +1698,7 @@
         <v>7077.91</v>
       </c>
       <c r="D3" s="27">
-        <f t="shared" ref="D3:D25" si="0">C3*115%</f>
+        <f t="shared" ref="D3:D23" si="0">C3*115%</f>
         <v>8139.5964999999997</v>
       </c>
       <c r="E3" s="32">
@@ -1780,7 +1774,7 @@
         <v>3277.4999999999995</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1803,7 +1797,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="26">
         <v>1</v>
@@ -1839,7 +1833,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="26">
         <v>1</v>
@@ -2004,7 +1998,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" s="26">
         <v>0</v>
@@ -2049,10 +2043,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="10" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B23" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="26">
         <v>0</v>
@@ -2065,178 +2059,182 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B24" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="26">
-        <v>0</v>
+        <v>669.81</v>
       </c>
       <c r="D24" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="33"/>
+        <f>C24*115%</f>
+        <v>770.28149999999982</v>
+      </c>
+      <c r="E24" s="32">
+        <v>1483.71</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B25" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="26">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="D25" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="33"/>
+        <f t="shared" ref="D25:D51" si="1">C25*115%</f>
+        <v>1086.75</v>
+      </c>
+      <c r="E25" s="32">
+        <v>1546.81</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="26">
         <v>1</v>
       </c>
       <c r="C26" s="26">
-        <v>669.81</v>
+        <v>1080</v>
       </c>
       <c r="D26" s="27">
-        <f>C26*115%</f>
-        <v>770.28149999999982</v>
+        <f t="shared" si="1"/>
+        <v>1242</v>
       </c>
       <c r="E26" s="32">
-        <v>1483.71</v>
+        <v>1391.04</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="26">
         <v>1</v>
       </c>
       <c r="C27" s="26">
-        <v>945</v>
+        <v>900</v>
       </c>
       <c r="D27" s="27">
-        <f t="shared" ref="D27:D53" si="1">C27*115%</f>
-        <v>1086.75</v>
-      </c>
-      <c r="E27" s="32">
-        <v>1546.81</v>
+        <f t="shared" si="1"/>
+        <v>1035</v>
+      </c>
+      <c r="E27" s="33">
+        <v>1159.2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28" s="26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" s="26">
-        <v>1080</v>
+        <v>292</v>
       </c>
       <c r="D28" s="27">
         <f t="shared" si="1"/>
-        <v>1242</v>
-      </c>
-      <c r="E28" s="32">
-        <v>1391.04</v>
+        <v>335.79999999999995</v>
+      </c>
+      <c r="E28" s="33">
+        <v>422.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="10" t="s">
-        <v>54</v>
+      <c r="A29" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="B29" s="26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="26">
-        <v>900</v>
+        <v>265.5</v>
       </c>
       <c r="D29" s="27">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>305.32499999999999</v>
       </c>
       <c r="E29" s="33">
-        <v>1159.2</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="10" t="s">
-        <v>55</v>
+      <c r="A30" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="B30" s="26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="26">
-        <v>292</v>
+        <v>260.10000000000002</v>
       </c>
       <c r="D30" s="27">
         <f t="shared" si="1"/>
-        <v>335.79999999999995</v>
+        <v>299.11500000000001</v>
       </c>
       <c r="E30" s="33">
-        <v>422.09</v>
+        <v>470.92</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" s="26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="26">
-        <v>265.5</v>
+        <v>359.1</v>
       </c>
       <c r="D31" s="27">
         <f t="shared" si="1"/>
-        <v>305.32499999999999</v>
+        <v>412.96499999999997</v>
       </c>
       <c r="E31" s="33">
-        <v>374.67</v>
+        <v>703.8</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B32" s="26">
         <v>2</v>
       </c>
       <c r="C32" s="26">
-        <v>260.10000000000002</v>
+        <v>359.62</v>
       </c>
       <c r="D32" s="27">
         <f t="shared" si="1"/>
-        <v>299.11500000000001</v>
+        <v>413.56299999999999</v>
       </c>
       <c r="E32" s="33">
-        <v>470.92</v>
+        <v>615.82000000000005</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B33" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="26">
-        <v>359.1</v>
+        <v>373.5</v>
       </c>
       <c r="D33" s="27">
         <f t="shared" si="1"/>
-        <v>412.96499999999997</v>
+        <v>429.52499999999998</v>
       </c>
       <c r="E33" s="33">
-        <v>703.8</v>
+        <v>516.47</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2247,14 +2245,14 @@
         <v>2</v>
       </c>
       <c r="C34" s="26">
-        <v>359.62</v>
+        <v>449.1</v>
       </c>
       <c r="D34" s="27">
         <f t="shared" si="1"/>
-        <v>413.56299999999999</v>
+        <v>516.46500000000003</v>
       </c>
       <c r="E34" s="33">
-        <v>615.82000000000005</v>
+        <v>516.47</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2262,197 +2260,197 @@
         <v>61</v>
       </c>
       <c r="B35" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="26">
-        <v>373.5</v>
+        <v>506</v>
       </c>
       <c r="D35" s="27">
         <f t="shared" si="1"/>
-        <v>429.52499999999998</v>
+        <v>581.9</v>
       </c>
       <c r="E35" s="33">
-        <v>516.47</v>
+        <v>883.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" s="26">
         <v>2</v>
       </c>
       <c r="C36" s="26">
-        <v>449.1</v>
+        <v>503.59</v>
       </c>
       <c r="D36" s="27">
         <f t="shared" si="1"/>
-        <v>516.46500000000003</v>
+        <v>579.12849999999992</v>
       </c>
       <c r="E36" s="33">
-        <v>516.47</v>
+        <v>902.75</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" s="26">
         <v>2</v>
       </c>
       <c r="C37" s="26">
-        <v>506</v>
+        <v>385.98</v>
       </c>
       <c r="D37" s="27">
         <f t="shared" si="1"/>
-        <v>581.9</v>
-      </c>
-      <c r="E37" s="33">
-        <v>883.2</v>
+        <v>443.87700000000001</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B38" s="26">
         <v>2</v>
       </c>
       <c r="C38" s="26">
-        <v>503.59</v>
+        <v>400</v>
       </c>
       <c r="D38" s="27">
         <f t="shared" si="1"/>
-        <v>579.12849999999992</v>
+        <v>459.99999999999994</v>
       </c>
       <c r="E38" s="33">
-        <v>902.75</v>
+        <v>869.4</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B39" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" s="26">
-        <v>385.98</v>
+        <v>890.44</v>
       </c>
       <c r="D39" s="27">
         <f t="shared" si="1"/>
-        <v>443.87700000000001</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>48</v>
+        <v>1024.0060000000001</v>
+      </c>
+      <c r="E39" s="33">
+        <v>1138.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="1" t="s">
-        <v>65</v>
+      <c r="A40" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="B40" s="26">
         <v>2</v>
       </c>
       <c r="C40" s="26">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="D40" s="27">
         <f t="shared" si="1"/>
-        <v>459.99999999999994</v>
+        <v>1265</v>
       </c>
       <c r="E40" s="33">
-        <v>869.4</v>
+        <v>1714.65</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="1" t="s">
-        <v>66</v>
+      <c r="A41" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="B41" s="26">
         <v>4</v>
       </c>
       <c r="C41" s="26">
-        <v>890.44</v>
+        <v>356.4</v>
       </c>
       <c r="D41" s="27">
         <f t="shared" si="1"/>
-        <v>1024.0060000000001</v>
+        <v>409.85999999999996</v>
       </c>
       <c r="E41" s="33">
-        <v>1138.5</v>
+        <v>624.01</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="8" t="s">
-        <v>67</v>
+      <c r="A42" s="28" t="s">
+        <v>68</v>
       </c>
       <c r="B42" s="26">
         <v>2</v>
       </c>
       <c r="C42" s="26">
-        <v>1100</v>
+        <v>348.3</v>
       </c>
       <c r="D42" s="27">
         <f t="shared" si="1"/>
-        <v>1265</v>
+        <v>400.54499999999996</v>
       </c>
       <c r="E42" s="33">
-        <v>1714.65</v>
+        <v>619.67999999999995</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B43" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="26">
-        <v>356.4</v>
+        <v>348.3</v>
       </c>
       <c r="D43" s="27">
         <f t="shared" si="1"/>
-        <v>409.85999999999996</v>
+        <v>400.54499999999996</v>
       </c>
       <c r="E43" s="33">
-        <v>624.01</v>
+        <v>612.88</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="28" t="s">
-        <v>69</v>
+      <c r="A44" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="B44" s="26">
         <v>2</v>
       </c>
       <c r="C44" s="26">
-        <v>348.3</v>
+        <v>486</v>
       </c>
       <c r="D44" s="27">
         <f t="shared" si="1"/>
-        <v>400.54499999999996</v>
+        <v>558.9</v>
       </c>
       <c r="E44" s="33">
-        <v>619.67999999999995</v>
+        <v>747.5</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B45" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45" s="26">
-        <v>348.3</v>
+        <v>495</v>
       </c>
       <c r="D45" s="27">
         <f t="shared" si="1"/>
-        <v>400.54499999999996</v>
+        <v>569.25</v>
       </c>
       <c r="E45" s="33">
-        <v>612.88</v>
+        <v>879.75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2460,177 +2458,175 @@
         <v>71</v>
       </c>
       <c r="B46" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C46" s="26">
-        <v>486</v>
+        <v>319.5</v>
       </c>
       <c r="D46" s="27">
         <f t="shared" si="1"/>
-        <v>558.9</v>
+        <v>367.42499999999995</v>
       </c>
       <c r="E46" s="33">
-        <v>747.5</v>
+        <v>708.97</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B47" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="26">
-        <v>495</v>
+        <v>355.4</v>
       </c>
       <c r="D47" s="27">
         <f t="shared" si="1"/>
-        <v>569.25</v>
+        <v>408.70999999999992</v>
       </c>
       <c r="E47" s="33">
-        <v>879.75</v>
+        <v>750.57</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B48" s="26">
         <v>4</v>
       </c>
       <c r="C48" s="26">
-        <v>319.5</v>
+        <v>498</v>
       </c>
       <c r="D48" s="27">
         <f t="shared" si="1"/>
-        <v>367.42499999999995</v>
+        <v>572.69999999999993</v>
       </c>
       <c r="E48" s="33">
-        <v>708.97</v>
+        <v>877.43</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B49" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" s="26">
-        <v>355.4</v>
+        <v>394.11</v>
       </c>
       <c r="D49" s="27">
         <f t="shared" si="1"/>
-        <v>408.70999999999992</v>
+        <v>453.22649999999999</v>
       </c>
       <c r="E49" s="33">
-        <v>750.57</v>
+        <v>568.22</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="26">
-        <v>4</v>
-      </c>
-      <c r="C50" s="26">
-        <v>498</v>
-      </c>
-      <c r="D50" s="27">
+        <v>75</v>
+      </c>
+      <c r="B50" s="33">
+        <v>1</v>
+      </c>
+      <c r="C50" s="32">
+        <v>258.3</v>
+      </c>
+      <c r="D50" s="32">
         <f t="shared" si="1"/>
-        <v>572.69999999999993</v>
-      </c>
-      <c r="E50" s="33">
-        <v>877.43</v>
+        <v>297.04500000000002</v>
+      </c>
+      <c r="E50" s="32">
+        <v>470.92</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="26">
-        <v>2</v>
-      </c>
-      <c r="C51" s="26">
-        <v>394.11</v>
-      </c>
-      <c r="D51" s="27">
+        <v>76</v>
+      </c>
+      <c r="B51" s="33">
+        <v>4</v>
+      </c>
+      <c r="C51" s="32">
+        <v>331.52</v>
+      </c>
+      <c r="D51" s="32">
         <f t="shared" si="1"/>
-        <v>453.22649999999999</v>
-      </c>
-      <c r="E51" s="33">
-        <v>568.22</v>
+        <v>381.24799999999993</v>
+      </c>
+      <c r="E51" s="32">
+        <v>608.87</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="33">
-        <v>1</v>
-      </c>
-      <c r="C52" s="32">
-        <v>258.3</v>
-      </c>
-      <c r="D52" s="32">
-        <f t="shared" si="1"/>
-        <v>297.04500000000002</v>
-      </c>
-      <c r="E52" s="32">
-        <v>470.92</v>
+        <v>78</v>
+      </c>
+      <c r="B52" s="27">
+        <v>5</v>
+      </c>
+      <c r="C52" s="26">
+        <v>1473.64</v>
+      </c>
+      <c r="D52" s="29">
+        <v>1934.56</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="10" t="s">
-        <v>77</v>
+      <c r="A53" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="B53" s="33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C53" s="32">
-        <v>331.52</v>
+        <v>184.79</v>
       </c>
       <c r="D53" s="32">
-        <f t="shared" si="1"/>
-        <v>381.24799999999993</v>
-      </c>
-      <c r="E53" s="32">
-        <v>608.87</v>
+        <v>230.99</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="33">
+        <v>10</v>
+      </c>
+      <c r="C54" s="32">
+        <v>233.87</v>
+      </c>
+      <c r="D54" s="32">
+        <v>304.04000000000002</v>
+      </c>
+      <c r="E54" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="27">
-        <v>5</v>
-      </c>
-      <c r="C54" s="26">
-        <v>1473.64</v>
-      </c>
-      <c r="D54" s="29">
-        <v>1934.56</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="31" t="s">
-        <v>82</v>
+      <c r="A55" s="34" t="s">
+        <v>83</v>
       </c>
       <c r="B55" s="33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C55" s="32">
-        <v>184.79</v>
+        <v>488.43</v>
       </c>
       <c r="D55" s="32">
-        <v>230.99</v>
+        <v>641.5</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2638,16 +2634,16 @@
         <v>84</v>
       </c>
       <c r="B56" s="33">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C56" s="32">
-        <v>233.87</v>
+        <v>259.60000000000002</v>
       </c>
       <c r="D56" s="32">
-        <v>304.04000000000002</v>
+        <v>337.5</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2655,16 +2651,16 @@
         <v>85</v>
       </c>
       <c r="B57" s="33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" s="32">
-        <v>488.43</v>
+        <v>275.02999999999997</v>
       </c>
       <c r="D57" s="32">
-        <v>641.5</v>
+        <v>357.53</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2675,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="C58" s="32">
-        <v>259.60000000000002</v>
+        <v>278.39999999999998</v>
       </c>
       <c r="D58" s="32">
-        <v>337.5</v>
+        <v>391.92</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2689,16 +2685,16 @@
         <v>87</v>
       </c>
       <c r="B59" s="33">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C59" s="32">
-        <v>275.02999999999997</v>
+        <v>215.48</v>
       </c>
       <c r="D59" s="32">
-        <v>357.53</v>
+        <v>280.12</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2706,16 +2702,16 @@
         <v>88</v>
       </c>
       <c r="B60" s="33">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C60" s="32">
-        <v>278.39999999999998</v>
+        <v>229.33</v>
       </c>
       <c r="D60" s="32">
-        <v>391.92</v>
+        <v>298.12</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2723,72 +2719,38 @@
         <v>89</v>
       </c>
       <c r="B61" s="33">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C61" s="32">
-        <v>215.48</v>
+        <v>2448.38</v>
       </c>
       <c r="D61" s="32">
-        <v>280.12</v>
+        <v>3182.89</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="34" t="s">
+      <c r="A62" s="35" t="s">
         <v>90</v>
       </c>
       <c r="B62" s="33">
-        <v>20</v>
-      </c>
-      <c r="C62" s="32">
-        <v>229.33</v>
+        <v>1</v>
+      </c>
+      <c r="C62" s="33">
+        <v>1516</v>
       </c>
       <c r="D62" s="32">
-        <v>298.12</v>
+        <v>1982.77</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="33">
-        <v>1</v>
-      </c>
-      <c r="C63" s="32">
-        <v>2448.38</v>
-      </c>
-      <c r="D63" s="32">
-        <v>3182.89</v>
-      </c>
-      <c r="E63" s="32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B64" s="33">
-        <v>1</v>
-      </c>
-      <c r="C64" s="33">
-        <v>1516</v>
-      </c>
-      <c r="D64" s="32">
-        <v>1982.77</v>
-      </c>
-      <c r="E64" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D54 D2:D51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D52 D2:D49">
       <formula1>DvListSource2</formula1>
     </dataValidation>
   </dataValidations>
